--- a/接口测试用例.xlsx
+++ b/接口测试用例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos-github\studyspace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D99D7A-70F9-47D0-A2AE-7B8CC3086FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF983313-3F02-4E20-B8B9-73AED05B0666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11873" yWindow="930" windowWidth="10274" windowHeight="13170" xr2:uid="{06184975-A5D6-452B-AD46-77C4DC04994E}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="16201" windowHeight="8393" xr2:uid="{06184975-A5D6-452B-AD46-77C4DC04994E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2175,10 +2175,10 @@
     <col min="4" max="4" width="13.796875" style="2" customWidth="1"/>
     <col min="5" max="5" width="36.6640625" customWidth="1"/>
     <col min="6" max="6" width="9.06640625" style="3"/>
-    <col min="7" max="7" width="15.19921875" customWidth="1"/>
+    <col min="7" max="7" width="18.46484375" customWidth="1"/>
     <col min="8" max="8" width="23.3984375" customWidth="1"/>
     <col min="9" max="9" width="22.73046875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="10" max="10" width="8.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -2209,7 +2209,7 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>66</v>
       </c>
       <c r="K1" s="6" t="s">
